--- a/templates/Cap_Huma_Modele_Import_Talents_VIERGE.xlsx
+++ b/templates/Cap_Huma_Modele_Import_Talents_VIERGE.xlsx
@@ -169,7 +169,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -222,8 +222,17 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
@@ -484,7 +493,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="100" customWidth="1" style="10" min="1" max="1"/>
@@ -531,7 +540,7 @@
     <row r="11" ht="23.85" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Prénom, Nom, Email et Code Pool sont obligatoires pour chaque ligne. Le Code Pool doit correspondre exactement à un pool déjà existant dans Cap Huma (vérifiable dans le tableau de bord) — une ligne avec un code pool inconnu sera rejetée.</t>
+          <t>Prénom, Nom et Email sont obligatoires pour chaque ligne. Code Pool est obligatoire UNIQUEMENT si la colonne Type de staff est vide ou vaut « Expatrié » — dans ce cas il doit correspondre exactement à un pool déjà existant dans Cap Huma. Pour un staff national (voir plus bas), laissez Code Pool vide.</t>
         </is>
       </c>
     </row>
@@ -563,43 +572,64 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>Staff national et Pool de suivi (colonnes Type de staff, Pool de suivi)</t>
+        </is>
+      </c>
+    </row>
     <row r="22" ht="15" customHeight="1" s="11">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>✅ Champ Statut — valeurs désormais confirmées (21/08/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="46.25" customHeight="1" s="11">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Les 4 valeurs exactes ont été confirmées en inspectant le filtre "Statut" de la page Talents de Cap Huma (source de vérité du code) : En poste ALIMA, En attente de poste, En poste autre ONG, En poste hors humanitaire. Une liste déroulante a été ajoutée sur cette colonne. Vous pouvez désormais la remplir en toute sécurité — une valeur hors liste fera toujours échouer la ligne, comme pour les autres champs à liste déroulante.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Laissez Type de staff vide (ou « Expatrié ») pour un import classique, comme avant. Pour importer un staff national : mettez « National » dans Type de staff, laissez Code Pool vide, et indiquez si besoin un pool dans Pool de suivi (le pool qui suit ce staff en vue d'une future validation — optionnel, doit correspondre à un pool existant si rempli). Une ligne avec à la fois Code Pool et Type de staff = National sera rejetée : les deux sont incompatibles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="46.25" customHeight="1" s="11"/>
+    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="11">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Champs volontairement absents de ce modèle</t>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>⚠️ Champ Statut — laisser vide</t>
         </is>
       </c>
     </row>
     <row r="28" ht="35.05" customHeight="1" s="11">
       <c r="A28" s="13" t="inlineStr">
         <is>
+          <t>Les 4 valeurs exactes acceptées par la base pour ce champ n'ont pas encore été confirmées avec certitude au moment de la création de ce modèle. Par sécurité, laissez cette colonne VIDE — chaque talent importé prendra automatiquement le statut par défaut (« En attente de poste »), et vous pourrez l'ajuster ensuite dans Cap Huma si besoin. Ne pas deviner de valeur : une valeur incorrecte ferait échouer l'import de la ligne entière.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31" ht="15" customHeight="1" s="11"/>
+    <row r="32" ht="23.85" customHeight="1" s="11">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>Champs volontairement absents de ce modèle</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
           <t>Certains champs de la fiche talent ne sont jamais importables en masse, par choix de sécurité : le statut de validité, la Liste Rouge, l'historique de statut, les documents confidentiels, et tout ce qui est calculé automatiquement par le site. Si un talent doit être signalé en Liste Rouge, cela reste une action manuelle dans Cap Huma après import, jamais via ce fichier.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="11">
-      <c r="A31" s="14" t="inlineStr">
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="14" t="inlineStr">
         <is>
           <t>Avant l'import définitif</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="23.85" customHeight="1" s="11">
-      <c r="A32" s="13" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Faites un premier essai avec 2 ou 3 lignes seulement, vérifiez le résultat dans Cap Huma, puis importez le reste. Ne partez jamais directement sur un fichier de 200 lignes sans avoir validé le format sur un petit échantillon.</t>
         </is>
@@ -618,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:X33"/>
+  <dimension ref="A1:Z33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="10" min="1" max="2"/>
@@ -640,6 +670,8 @@
     <col width="14" customWidth="1" style="10" min="20" max="22"/>
     <col width="10" customWidth="1" style="10" min="23" max="23"/>
     <col width="16" customWidth="1" style="10" min="24" max="24"/>
+    <col width="8" customWidth="1" style="11" min="25" max="25"/>
+    <col width="8" customWidth="1" style="11" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="33.75" customHeight="1" s="11">
@@ -663,1114 +695,1140 @@
           <t>Code Pool*</t>
         </is>
       </c>
-      <c r="E1" s="17" t="inlineStr">
+      <c r="E1" s="18" t="inlineStr">
         <is>
           <t>Genre</t>
         </is>
       </c>
-      <c r="F1" s="17" t="inlineStr">
+      <c r="F1" s="18" t="inlineStr">
         <is>
           <t>Nationalité</t>
         </is>
       </c>
-      <c r="G1" s="17" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Pays de résidence</t>
         </is>
       </c>
-      <c r="H1" s="17" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>Fonction actuelle</t>
         </is>
       </c>
-      <c r="I1" s="17" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>Niveau d'études</t>
         </is>
       </c>
-      <c r="J1" s="17" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>Spécialité</t>
         </is>
       </c>
-      <c r="K1" s="17" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>Langues parlées</t>
         </is>
       </c>
-      <c r="L1" s="17" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>Autres langues</t>
         </is>
       </c>
-      <c r="M1" s="17" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>Compétences clés</t>
         </is>
       </c>
-      <c r="N1" s="17" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>Contextes d'intervention</t>
         </is>
       </c>
-      <c r="O1" s="17" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>Zones d'intervention</t>
         </is>
       </c>
-      <c r="P1" s="17" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>Visa valide ?</t>
         </is>
       </c>
-      <c r="Q1" s="17" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>Date d'intégration au pool</t>
         </is>
       </c>
-      <c r="R1" s="17" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>Expérience ALIMA (mois)</t>
         </is>
       </c>
-      <c r="S1" s="17" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>Expérience humanitaire (mois)</t>
         </is>
       </c>
-      <c r="T1" s="17" t="inlineStr">
+      <c r="T1" s="18" t="inlineStr">
         <is>
           <t>Nombre de missions ALIMA</t>
         </is>
       </c>
-      <c r="U1" s="17" t="inlineStr">
+      <c r="U1" s="18" t="inlineStr">
         <is>
           <t>Type de disponibilité</t>
         </is>
       </c>
-      <c r="V1" s="17" t="inlineStr">
+      <c r="V1" s="18" t="inlineStr">
         <is>
           <t>Date de disponibilité</t>
         </is>
       </c>
-      <c r="W1" s="17" t="inlineStr">
+      <c r="W1" s="18" t="inlineStr">
         <is>
           <t>Préavis (mois)</t>
         </is>
       </c>
-      <c r="X1" s="17" t="inlineStr">
+      <c r="X1" s="18" t="inlineStr">
         <is>
           <t>Statut (laisser vide)</t>
         </is>
       </c>
+      <c r="Y1" s="18" t="inlineStr">
+        <is>
+          <t>Type de staff</t>
+        </is>
+      </c>
+      <c r="Z1" s="18" t="inlineStr">
+        <is>
+          <t>Pool de suivi</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="12" customHeight="1" s="11">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="20" t="inlineStr">
         <is>
           <t>first_name</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>last_name</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="20" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="20" t="inlineStr">
         <is>
           <t>pool</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="20" t="inlineStr">
         <is>
           <t>gender</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="20" t="inlineStr">
         <is>
           <t>nationality</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>country_of_residence</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>current_function</t>
         </is>
       </c>
-      <c r="I2" s="18" t="inlineStr">
+      <c r="I2" s="20" t="inlineStr">
         <is>
           <t>education_level</t>
         </is>
       </c>
-      <c r="J2" s="18" t="inlineStr">
+      <c r="J2" s="20" t="inlineStr">
         <is>
           <t>education_specialty</t>
         </is>
       </c>
-      <c r="K2" s="18" t="inlineStr">
+      <c r="K2" s="20" t="inlineStr">
         <is>
           <t>languages</t>
         </is>
       </c>
-      <c r="L2" s="18" t="inlineStr">
+      <c r="L2" s="20" t="inlineStr">
         <is>
           <t>other_languages</t>
         </is>
       </c>
-      <c r="M2" s="18" t="inlineStr">
+      <c r="M2" s="20" t="inlineStr">
         <is>
           <t>key_skills</t>
         </is>
       </c>
-      <c r="N2" s="18" t="inlineStr">
+      <c r="N2" s="20" t="inlineStr">
         <is>
           <t>intervention_contexts</t>
         </is>
       </c>
-      <c r="O2" s="18" t="inlineStr">
+      <c r="O2" s="20" t="inlineStr">
         <is>
           <t>intervention_zones</t>
         </is>
       </c>
-      <c r="P2" s="18" t="inlineStr">
+      <c r="P2" s="20" t="inlineStr">
         <is>
           <t>has_visa</t>
         </is>
       </c>
-      <c r="Q2" s="18" t="inlineStr">
+      <c r="Q2" s="20" t="inlineStr">
         <is>
           <t>pool_integration_date</t>
         </is>
       </c>
-      <c r="R2" s="18" t="inlineStr">
+      <c r="R2" s="20" t="inlineStr">
         <is>
           <t>experience_months_alima</t>
         </is>
       </c>
-      <c r="S2" s="18" t="inlineStr">
+      <c r="S2" s="20" t="inlineStr">
         <is>
           <t>experience_months_humanitarian</t>
         </is>
       </c>
-      <c r="T2" s="18" t="inlineStr">
+      <c r="T2" s="20" t="inlineStr">
         <is>
           <t>number_of_alima_missions</t>
         </is>
       </c>
-      <c r="U2" s="18" t="inlineStr">
+      <c r="U2" s="20" t="inlineStr">
         <is>
           <t>availability_type</t>
         </is>
       </c>
-      <c r="V2" s="18" t="inlineStr">
+      <c r="V2" s="20" t="inlineStr">
         <is>
           <t>availability_date</t>
         </is>
       </c>
-      <c r="W2" s="18" t="inlineStr">
+      <c r="W2" s="20" t="inlineStr">
         <is>
           <t>availability_months</t>
         </is>
       </c>
-      <c r="X2" s="18" t="inlineStr">
+      <c r="X2" s="20" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
+      <c r="Y2" s="20" t="inlineStr">
+        <is>
+          <t>staff_type</t>
+        </is>
+      </c>
+      <c r="Z2" s="20" t="inlineStr">
+        <is>
+          <t>tracking_pool</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="11">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>Awa</t>
         </is>
       </c>
-      <c r="B3" s="19" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>Ndiaye</t>
         </is>
       </c>
-      <c r="C3" s="19" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t>awa.ndiaye@example.com</t>
         </is>
       </c>
-      <c r="D3" s="19" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>COLOG</t>
         </is>
       </c>
-      <c r="E3" s="19" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="F3" s="19" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>Sénégalaise</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>Sénégal</t>
         </is>
       </c>
-      <c r="H3" s="19" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>Logisticienne</t>
         </is>
       </c>
-      <c r="I3" s="19" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t>bac+5</t>
         </is>
       </c>
-      <c r="J3" s="19" t="inlineStr">
+      <c r="J3" s="22" t="inlineStr">
         <is>
           <t>Logistique humanitaire</t>
         </is>
       </c>
-      <c r="K3" s="19" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t>Français, Wolof, Anglais</t>
         </is>
       </c>
-      <c r="L3" s="19" t="n"/>
-      <c r="M3" s="19" t="inlineStr">
+      <c r="L3" s="22" t="n"/>
+      <c r="M3" s="22" t="inlineStr">
         <is>
           <t>Logistique, Gestion de stock</t>
         </is>
       </c>
-      <c r="N3" s="19" t="inlineStr">
+      <c r="N3" s="22" t="inlineStr">
         <is>
           <t>Urgence, Conflit</t>
         </is>
       </c>
-      <c r="O3" s="19" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
         <is>
           <t>Sahel, Afrique de l'Ouest</t>
         </is>
       </c>
-      <c r="P3" s="19" t="inlineStr">
+      <c r="P3" s="22" t="inlineStr">
         <is>
           <t>Non</t>
         </is>
       </c>
-      <c r="Q3" s="19" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t>2026-01-15</t>
         </is>
       </c>
-      <c r="R3" s="19" t="inlineStr">
+      <c r="R3" s="22" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S3" s="19" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="T3" s="19" t="inlineStr">
+      <c r="T3" s="22" t="inlineStr">
         <is>
           <t>2 missions</t>
         </is>
       </c>
-      <c r="U3" s="19" t="inlineStr">
+      <c r="U3" s="22" t="inlineStr">
         <is>
           <t>Immédiate</t>
         </is>
       </c>
-      <c r="V3" s="19" t="n"/>
-      <c r="W3" s="19" t="n"/>
-      <c r="X3" s="19" t="n"/>
+      <c r="V3" s="22" t="n"/>
+      <c r="W3" s="22" t="n"/>
+      <c r="X3" s="22" t="n"/>
+      <c r="Y3" s="22" t="inlineStr">
+        <is>
+          <t>Expatrié</t>
+        </is>
+      </c>
+      <c r="Z3" s="22" t="inlineStr"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="11">
-      <c r="A4" s="20" t="n"/>
-      <c r="B4" s="20" t="n"/>
-      <c r="C4" s="20" t="n"/>
-      <c r="D4" s="20" t="n"/>
-      <c r="E4" s="20" t="n"/>
-      <c r="F4" s="20" t="n"/>
-      <c r="G4" s="20" t="n"/>
-      <c r="H4" s="20" t="n"/>
-      <c r="I4" s="20" t="n"/>
-      <c r="J4" s="20" t="n"/>
-      <c r="K4" s="20" t="n"/>
-      <c r="L4" s="20" t="n"/>
-      <c r="M4" s="20" t="n"/>
-      <c r="N4" s="20" t="n"/>
-      <c r="O4" s="20" t="n"/>
-      <c r="P4" s="20" t="n"/>
-      <c r="Q4" s="20" t="n"/>
-      <c r="R4" s="20" t="n"/>
-      <c r="S4" s="20" t="n"/>
-      <c r="T4" s="20" t="n"/>
-      <c r="U4" s="20" t="n"/>
-      <c r="V4" s="20" t="n"/>
-      <c r="W4" s="20" t="n"/>
-      <c r="X4" s="20" t="n"/>
+      <c r="A4" s="23" t="n"/>
+      <c r="B4" s="23" t="n"/>
+      <c r="C4" s="23" t="n"/>
+      <c r="D4" s="23" t="n"/>
+      <c r="E4" s="23" t="n"/>
+      <c r="F4" s="23" t="n"/>
+      <c r="G4" s="23" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="23" t="n"/>
+      <c r="J4" s="23" t="n"/>
+      <c r="K4" s="23" t="n"/>
+      <c r="L4" s="23" t="n"/>
+      <c r="M4" s="23" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="23" t="n"/>
+      <c r="S4" s="23" t="n"/>
+      <c r="T4" s="23" t="n"/>
+      <c r="U4" s="23" t="n"/>
+      <c r="V4" s="23" t="n"/>
+      <c r="W4" s="23" t="n"/>
+      <c r="X4" s="23" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1" s="11">
-      <c r="A5" s="20" t="n"/>
-      <c r="B5" s="20" t="n"/>
-      <c r="C5" s="20" t="n"/>
-      <c r="D5" s="20" t="n"/>
-      <c r="E5" s="20" t="n"/>
-      <c r="F5" s="20" t="n"/>
-      <c r="G5" s="20" t="n"/>
-      <c r="H5" s="20" t="n"/>
-      <c r="I5" s="20" t="n"/>
-      <c r="J5" s="20" t="n"/>
-      <c r="K5" s="20" t="n"/>
-      <c r="L5" s="20" t="n"/>
-      <c r="M5" s="20" t="n"/>
-      <c r="N5" s="20" t="n"/>
-      <c r="O5" s="20" t="n"/>
-      <c r="P5" s="20" t="n"/>
-      <c r="Q5" s="20" t="n"/>
-      <c r="R5" s="20" t="n"/>
-      <c r="S5" s="20" t="n"/>
-      <c r="T5" s="20" t="n"/>
-      <c r="U5" s="20" t="n"/>
-      <c r="V5" s="20" t="n"/>
-      <c r="W5" s="20" t="n"/>
-      <c r="X5" s="20" t="n"/>
+      <c r="A5" s="23" t="n"/>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="23" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="23" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="23" t="n"/>
+      <c r="M5" s="23" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="23" t="n"/>
+      <c r="S5" s="23" t="n"/>
+      <c r="T5" s="23" t="n"/>
+      <c r="U5" s="23" t="n"/>
+      <c r="V5" s="23" t="n"/>
+      <c r="W5" s="23" t="n"/>
+      <c r="X5" s="23" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="11">
-      <c r="A6" s="20" t="n"/>
-      <c r="B6" s="20" t="n"/>
-      <c r="C6" s="20" t="n"/>
-      <c r="D6" s="20" t="n"/>
-      <c r="E6" s="20" t="n"/>
-      <c r="F6" s="20" t="n"/>
-      <c r="G6" s="20" t="n"/>
-      <c r="H6" s="20" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="20" t="n"/>
-      <c r="K6" s="20" t="n"/>
-      <c r="L6" s="20" t="n"/>
-      <c r="M6" s="20" t="n"/>
-      <c r="N6" s="20" t="n"/>
-      <c r="O6" s="20" t="n"/>
-      <c r="P6" s="20" t="n"/>
-      <c r="Q6" s="20" t="n"/>
-      <c r="R6" s="20" t="n"/>
-      <c r="S6" s="20" t="n"/>
-      <c r="T6" s="20" t="n"/>
-      <c r="U6" s="20" t="n"/>
-      <c r="V6" s="20" t="n"/>
-      <c r="W6" s="20" t="n"/>
-      <c r="X6" s="20" t="n"/>
+      <c r="A6" s="23" t="n"/>
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="23" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="23" t="n"/>
+      <c r="L6" s="23" t="n"/>
+      <c r="M6" s="23" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="23" t="n"/>
+      <c r="S6" s="23" t="n"/>
+      <c r="T6" s="23" t="n"/>
+      <c r="U6" s="23" t="n"/>
+      <c r="V6" s="23" t="n"/>
+      <c r="W6" s="23" t="n"/>
+      <c r="X6" s="23" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="11">
-      <c r="A7" s="20" t="n"/>
-      <c r="B7" s="20" t="n"/>
-      <c r="C7" s="20" t="n"/>
-      <c r="D7" s="20" t="n"/>
-      <c r="E7" s="20" t="n"/>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="20" t="n"/>
-      <c r="P7" s="20" t="n"/>
-      <c r="Q7" s="20" t="n"/>
-      <c r="R7" s="20" t="n"/>
-      <c r="S7" s="20" t="n"/>
-      <c r="T7" s="20" t="n"/>
-      <c r="U7" s="20" t="n"/>
-      <c r="V7" s="20" t="n"/>
-      <c r="W7" s="20" t="n"/>
-      <c r="X7" s="20" t="n"/>
+      <c r="A7" s="23" t="n"/>
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="23" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="23" t="n"/>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="23" t="n"/>
+      <c r="S7" s="23" t="n"/>
+      <c r="T7" s="23" t="n"/>
+      <c r="U7" s="23" t="n"/>
+      <c r="V7" s="23" t="n"/>
+      <c r="W7" s="23" t="n"/>
+      <c r="X7" s="23" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1" s="11">
-      <c r="A8" s="20" t="n"/>
-      <c r="B8" s="20" t="n"/>
-      <c r="C8" s="20" t="n"/>
-      <c r="D8" s="20" t="n"/>
-      <c r="E8" s="20" t="n"/>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="20" t="n"/>
-      <c r="P8" s="20" t="n"/>
-      <c r="Q8" s="20" t="n"/>
-      <c r="R8" s="20" t="n"/>
-      <c r="S8" s="20" t="n"/>
-      <c r="T8" s="20" t="n"/>
-      <c r="U8" s="20" t="n"/>
-      <c r="V8" s="20" t="n"/>
-      <c r="W8" s="20" t="n"/>
-      <c r="X8" s="20" t="n"/>
+      <c r="A8" s="23" t="n"/>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="23" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="23" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="23" t="n"/>
+      <c r="S8" s="23" t="n"/>
+      <c r="T8" s="23" t="n"/>
+      <c r="U8" s="23" t="n"/>
+      <c r="V8" s="23" t="n"/>
+      <c r="W8" s="23" t="n"/>
+      <c r="X8" s="23" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="11">
-      <c r="A9" s="20" t="n"/>
-      <c r="B9" s="20" t="n"/>
-      <c r="C9" s="20" t="n"/>
-      <c r="D9" s="20" t="n"/>
-      <c r="E9" s="20" t="n"/>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="20" t="n"/>
-      <c r="P9" s="20" t="n"/>
-      <c r="Q9" s="20" t="n"/>
-      <c r="R9" s="20" t="n"/>
-      <c r="S9" s="20" t="n"/>
-      <c r="T9" s="20" t="n"/>
-      <c r="U9" s="20" t="n"/>
-      <c r="V9" s="20" t="n"/>
-      <c r="W9" s="20" t="n"/>
-      <c r="X9" s="20" t="n"/>
+      <c r="A9" s="23" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="23" t="n"/>
+      <c r="L9" s="23" t="n"/>
+      <c r="M9" s="23" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="23" t="n"/>
+      <c r="S9" s="23" t="n"/>
+      <c r="T9" s="23" t="n"/>
+      <c r="U9" s="23" t="n"/>
+      <c r="V9" s="23" t="n"/>
+      <c r="W9" s="23" t="n"/>
+      <c r="X9" s="23" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="11">
-      <c r="A10" s="20" t="n"/>
-      <c r="B10" s="20" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
-      <c r="E10" s="20" t="n"/>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="20" t="n"/>
-      <c r="P10" s="20" t="n"/>
-      <c r="Q10" s="20" t="n"/>
-      <c r="R10" s="20" t="n"/>
-      <c r="S10" s="20" t="n"/>
-      <c r="T10" s="20" t="n"/>
-      <c r="U10" s="20" t="n"/>
-      <c r="V10" s="20" t="n"/>
-      <c r="W10" s="20" t="n"/>
-      <c r="X10" s="20" t="n"/>
+      <c r="A10" s="23" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="23" t="n"/>
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="23" t="n"/>
+      <c r="S10" s="23" t="n"/>
+      <c r="T10" s="23" t="n"/>
+      <c r="U10" s="23" t="n"/>
+      <c r="V10" s="23" t="n"/>
+      <c r="W10" s="23" t="n"/>
+      <c r="X10" s="23" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="11">
-      <c r="A11" s="20" t="n"/>
-      <c r="B11" s="20" t="n"/>
-      <c r="C11" s="20" t="n"/>
-      <c r="D11" s="20" t="n"/>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="20" t="n"/>
-      <c r="P11" s="20" t="n"/>
-      <c r="Q11" s="20" t="n"/>
-      <c r="R11" s="20" t="n"/>
-      <c r="S11" s="20" t="n"/>
-      <c r="T11" s="20" t="n"/>
-      <c r="U11" s="20" t="n"/>
-      <c r="V11" s="20" t="n"/>
-      <c r="W11" s="20" t="n"/>
-      <c r="X11" s="20" t="n"/>
+      <c r="A11" s="23" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="23" t="n"/>
+      <c r="L11" s="23" t="n"/>
+      <c r="M11" s="23" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="23" t="n"/>
+      <c r="S11" s="23" t="n"/>
+      <c r="T11" s="23" t="n"/>
+      <c r="U11" s="23" t="n"/>
+      <c r="V11" s="23" t="n"/>
+      <c r="W11" s="23" t="n"/>
+      <c r="X11" s="23" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="11">
-      <c r="A12" s="20" t="n"/>
-      <c r="B12" s="20" t="n"/>
-      <c r="C12" s="20" t="n"/>
-      <c r="D12" s="20" t="n"/>
-      <c r="E12" s="20" t="n"/>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="20" t="n"/>
-      <c r="P12" s="20" t="n"/>
-      <c r="Q12" s="20" t="n"/>
-      <c r="R12" s="20" t="n"/>
-      <c r="S12" s="20" t="n"/>
-      <c r="T12" s="20" t="n"/>
-      <c r="U12" s="20" t="n"/>
-      <c r="V12" s="20" t="n"/>
-      <c r="W12" s="20" t="n"/>
-      <c r="X12" s="20" t="n"/>
+      <c r="A12" s="23" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="23" t="n"/>
+      <c r="L12" s="23" t="n"/>
+      <c r="M12" s="23" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+      <c r="R12" s="23" t="n"/>
+      <c r="S12" s="23" t="n"/>
+      <c r="T12" s="23" t="n"/>
+      <c r="U12" s="23" t="n"/>
+      <c r="V12" s="23" t="n"/>
+      <c r="W12" s="23" t="n"/>
+      <c r="X12" s="23" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="11">
-      <c r="A13" s="20" t="n"/>
-      <c r="B13" s="20" t="n"/>
-      <c r="C13" s="20" t="n"/>
-      <c r="D13" s="20" t="n"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="20" t="n"/>
-      <c r="P13" s="20" t="n"/>
-      <c r="Q13" s="20" t="n"/>
-      <c r="R13" s="20" t="n"/>
-      <c r="S13" s="20" t="n"/>
-      <c r="T13" s="20" t="n"/>
-      <c r="U13" s="20" t="n"/>
-      <c r="V13" s="20" t="n"/>
-      <c r="W13" s="20" t="n"/>
-      <c r="X13" s="20" t="n"/>
+      <c r="A13" s="23" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="23" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="23" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+      <c r="R13" s="23" t="n"/>
+      <c r="S13" s="23" t="n"/>
+      <c r="T13" s="23" t="n"/>
+      <c r="U13" s="23" t="n"/>
+      <c r="V13" s="23" t="n"/>
+      <c r="W13" s="23" t="n"/>
+      <c r="X13" s="23" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="11">
-      <c r="A14" s="20" t="n"/>
-      <c r="B14" s="20" t="n"/>
-      <c r="C14" s="20" t="n"/>
-      <c r="D14" s="20" t="n"/>
-      <c r="E14" s="20" t="n"/>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="20" t="n"/>
-      <c r="O14" s="20" t="n"/>
-      <c r="P14" s="20" t="n"/>
-      <c r="Q14" s="20" t="n"/>
-      <c r="R14" s="20" t="n"/>
-      <c r="S14" s="20" t="n"/>
-      <c r="T14" s="20" t="n"/>
-      <c r="U14" s="20" t="n"/>
-      <c r="V14" s="20" t="n"/>
-      <c r="W14" s="20" t="n"/>
-      <c r="X14" s="20" t="n"/>
+      <c r="A14" s="23" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
+      <c r="I14" s="23" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="23" t="n"/>
+      <c r="L14" s="23" t="n"/>
+      <c r="M14" s="23" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="23" t="n"/>
+      <c r="S14" s="23" t="n"/>
+      <c r="T14" s="23" t="n"/>
+      <c r="U14" s="23" t="n"/>
+      <c r="V14" s="23" t="n"/>
+      <c r="W14" s="23" t="n"/>
+      <c r="X14" s="23" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="11">
-      <c r="A15" s="20" t="n"/>
-      <c r="B15" s="20" t="n"/>
-      <c r="C15" s="20" t="n"/>
-      <c r="D15" s="20" t="n"/>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="20" t="n"/>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="20" t="n"/>
-      <c r="O15" s="20" t="n"/>
-      <c r="P15" s="20" t="n"/>
-      <c r="Q15" s="20" t="n"/>
-      <c r="R15" s="20" t="n"/>
-      <c r="S15" s="20" t="n"/>
-      <c r="T15" s="20" t="n"/>
-      <c r="U15" s="20" t="n"/>
-      <c r="V15" s="20" t="n"/>
-      <c r="W15" s="20" t="n"/>
-      <c r="X15" s="20" t="n"/>
+      <c r="A15" s="23" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+      <c r="H15" s="23" t="n"/>
+      <c r="I15" s="23" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="23" t="n"/>
+      <c r="L15" s="23" t="n"/>
+      <c r="M15" s="23" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="23" t="n"/>
+      <c r="S15" s="23" t="n"/>
+      <c r="T15" s="23" t="n"/>
+      <c r="U15" s="23" t="n"/>
+      <c r="V15" s="23" t="n"/>
+      <c r="W15" s="23" t="n"/>
+      <c r="X15" s="23" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="11">
-      <c r="A16" s="20" t="n"/>
-      <c r="B16" s="20" t="n"/>
-      <c r="C16" s="20" t="n"/>
-      <c r="D16" s="20" t="n"/>
-      <c r="E16" s="20" t="n"/>
-      <c r="F16" s="20" t="n"/>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="20" t="n"/>
-      <c r="I16" s="20" t="n"/>
-      <c r="J16" s="20" t="n"/>
-      <c r="K16" s="20" t="n"/>
-      <c r="L16" s="20" t="n"/>
-      <c r="M16" s="20" t="n"/>
-      <c r="N16" s="20" t="n"/>
-      <c r="O16" s="20" t="n"/>
-      <c r="P16" s="20" t="n"/>
-      <c r="Q16" s="20" t="n"/>
-      <c r="R16" s="20" t="n"/>
-      <c r="S16" s="20" t="n"/>
-      <c r="T16" s="20" t="n"/>
-      <c r="U16" s="20" t="n"/>
-      <c r="V16" s="20" t="n"/>
-      <c r="W16" s="20" t="n"/>
-      <c r="X16" s="20" t="n"/>
+      <c r="A16" s="23" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+      <c r="H16" s="23" t="n"/>
+      <c r="I16" s="23" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="23" t="n"/>
+      <c r="L16" s="23" t="n"/>
+      <c r="M16" s="23" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+      <c r="R16" s="23" t="n"/>
+      <c r="S16" s="23" t="n"/>
+      <c r="T16" s="23" t="n"/>
+      <c r="U16" s="23" t="n"/>
+      <c r="V16" s="23" t="n"/>
+      <c r="W16" s="23" t="n"/>
+      <c r="X16" s="23" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="11">
-      <c r="A17" s="20" t="n"/>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="20" t="n"/>
-      <c r="D17" s="20" t="n"/>
-      <c r="E17" s="20" t="n"/>
-      <c r="F17" s="20" t="n"/>
-      <c r="G17" s="20" t="n"/>
-      <c r="H17" s="20" t="n"/>
-      <c r="I17" s="20" t="n"/>
-      <c r="J17" s="20" t="n"/>
-      <c r="K17" s="20" t="n"/>
-      <c r="L17" s="20" t="n"/>
-      <c r="M17" s="20" t="n"/>
-      <c r="N17" s="20" t="n"/>
-      <c r="O17" s="20" t="n"/>
-      <c r="P17" s="20" t="n"/>
-      <c r="Q17" s="20" t="n"/>
-      <c r="R17" s="20" t="n"/>
-      <c r="S17" s="20" t="n"/>
-      <c r="T17" s="20" t="n"/>
-      <c r="U17" s="20" t="n"/>
-      <c r="V17" s="20" t="n"/>
-      <c r="W17" s="20" t="n"/>
-      <c r="X17" s="20" t="n"/>
+      <c r="A17" s="23" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+      <c r="H17" s="23" t="n"/>
+      <c r="I17" s="23" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="23" t="n"/>
+      <c r="L17" s="23" t="n"/>
+      <c r="M17" s="23" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+      <c r="R17" s="23" t="n"/>
+      <c r="S17" s="23" t="n"/>
+      <c r="T17" s="23" t="n"/>
+      <c r="U17" s="23" t="n"/>
+      <c r="V17" s="23" t="n"/>
+      <c r="W17" s="23" t="n"/>
+      <c r="X17" s="23" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="11">
-      <c r="A18" s="20" t="n"/>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="20" t="n"/>
-      <c r="D18" s="20" t="n"/>
-      <c r="E18" s="20" t="n"/>
-      <c r="F18" s="20" t="n"/>
-      <c r="G18" s="20" t="n"/>
-      <c r="H18" s="20" t="n"/>
-      <c r="I18" s="20" t="n"/>
-      <c r="J18" s="20" t="n"/>
-      <c r="K18" s="20" t="n"/>
-      <c r="L18" s="20" t="n"/>
-      <c r="M18" s="20" t="n"/>
-      <c r="N18" s="20" t="n"/>
-      <c r="O18" s="20" t="n"/>
-      <c r="P18" s="20" t="n"/>
-      <c r="Q18" s="20" t="n"/>
-      <c r="R18" s="20" t="n"/>
-      <c r="S18" s="20" t="n"/>
-      <c r="T18" s="20" t="n"/>
-      <c r="U18" s="20" t="n"/>
-      <c r="V18" s="20" t="n"/>
-      <c r="W18" s="20" t="n"/>
-      <c r="X18" s="20" t="n"/>
+      <c r="A18" s="23" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+      <c r="H18" s="23" t="n"/>
+      <c r="I18" s="23" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="23" t="n"/>
+      <c r="L18" s="23" t="n"/>
+      <c r="M18" s="23" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+      <c r="R18" s="23" t="n"/>
+      <c r="S18" s="23" t="n"/>
+      <c r="T18" s="23" t="n"/>
+      <c r="U18" s="23" t="n"/>
+      <c r="V18" s="23" t="n"/>
+      <c r="W18" s="23" t="n"/>
+      <c r="X18" s="23" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="11">
-      <c r="A19" s="20" t="n"/>
-      <c r="B19" s="20" t="n"/>
-      <c r="C19" s="20" t="n"/>
-      <c r="D19" s="20" t="n"/>
-      <c r="E19" s="20" t="n"/>
-      <c r="F19" s="20" t="n"/>
-      <c r="G19" s="20" t="n"/>
-      <c r="H19" s="20" t="n"/>
-      <c r="I19" s="20" t="n"/>
-      <c r="J19" s="20" t="n"/>
-      <c r="K19" s="20" t="n"/>
-      <c r="L19" s="20" t="n"/>
-      <c r="M19" s="20" t="n"/>
-      <c r="N19" s="20" t="n"/>
-      <c r="O19" s="20" t="n"/>
-      <c r="P19" s="20" t="n"/>
-      <c r="Q19" s="20" t="n"/>
-      <c r="R19" s="20" t="n"/>
-      <c r="S19" s="20" t="n"/>
-      <c r="T19" s="20" t="n"/>
-      <c r="U19" s="20" t="n"/>
-      <c r="V19" s="20" t="n"/>
-      <c r="W19" s="20" t="n"/>
-      <c r="X19" s="20" t="n"/>
+      <c r="A19" s="23" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="23" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="23" t="n"/>
+      <c r="L19" s="23" t="n"/>
+      <c r="M19" s="23" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="23" t="n"/>
+      <c r="S19" s="23" t="n"/>
+      <c r="T19" s="23" t="n"/>
+      <c r="U19" s="23" t="n"/>
+      <c r="V19" s="23" t="n"/>
+      <c r="W19" s="23" t="n"/>
+      <c r="X19" s="23" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="11">
-      <c r="A20" s="20" t="n"/>
-      <c r="B20" s="20" t="n"/>
-      <c r="C20" s="20" t="n"/>
-      <c r="D20" s="20" t="n"/>
-      <c r="E20" s="20" t="n"/>
-      <c r="F20" s="20" t="n"/>
-      <c r="G20" s="20" t="n"/>
-      <c r="H20" s="20" t="n"/>
-      <c r="I20" s="20" t="n"/>
-      <c r="J20" s="20" t="n"/>
-      <c r="K20" s="20" t="n"/>
-      <c r="L20" s="20" t="n"/>
-      <c r="M20" s="20" t="n"/>
-      <c r="N20" s="20" t="n"/>
-      <c r="O20" s="20" t="n"/>
-      <c r="P20" s="20" t="n"/>
-      <c r="Q20" s="20" t="n"/>
-      <c r="R20" s="20" t="n"/>
-      <c r="S20" s="20" t="n"/>
-      <c r="T20" s="20" t="n"/>
-      <c r="U20" s="20" t="n"/>
-      <c r="V20" s="20" t="n"/>
-      <c r="W20" s="20" t="n"/>
-      <c r="X20" s="20" t="n"/>
+      <c r="A20" s="23" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+      <c r="H20" s="23" t="n"/>
+      <c r="I20" s="23" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="23" t="n"/>
+      <c r="L20" s="23" t="n"/>
+      <c r="M20" s="23" t="n"/>
+      <c r="N20" s="23" t="n"/>
+      <c r="O20" s="23" t="n"/>
+      <c r="P20" s="23" t="n"/>
+      <c r="Q20" s="23" t="n"/>
+      <c r="R20" s="23" t="n"/>
+      <c r="S20" s="23" t="n"/>
+      <c r="T20" s="23" t="n"/>
+      <c r="U20" s="23" t="n"/>
+      <c r="V20" s="23" t="n"/>
+      <c r="W20" s="23" t="n"/>
+      <c r="X20" s="23" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="11">
-      <c r="A21" s="20" t="n"/>
-      <c r="B21" s="20" t="n"/>
-      <c r="C21" s="20" t="n"/>
-      <c r="D21" s="20" t="n"/>
-      <c r="E21" s="20" t="n"/>
-      <c r="F21" s="20" t="n"/>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
-      <c r="I21" s="20" t="n"/>
-      <c r="J21" s="20" t="n"/>
-      <c r="K21" s="20" t="n"/>
-      <c r="L21" s="20" t="n"/>
-      <c r="M21" s="20" t="n"/>
-      <c r="N21" s="20" t="n"/>
-      <c r="O21" s="20" t="n"/>
-      <c r="P21" s="20" t="n"/>
-      <c r="Q21" s="20" t="n"/>
-      <c r="R21" s="20" t="n"/>
-      <c r="S21" s="20" t="n"/>
-      <c r="T21" s="20" t="n"/>
-      <c r="U21" s="20" t="n"/>
-      <c r="V21" s="20" t="n"/>
-      <c r="W21" s="20" t="n"/>
-      <c r="X21" s="20" t="n"/>
+      <c r="A21" s="23" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+      <c r="L21" s="23" t="n"/>
+      <c r="M21" s="23" t="n"/>
+      <c r="N21" s="23" t="n"/>
+      <c r="O21" s="23" t="n"/>
+      <c r="P21" s="23" t="n"/>
+      <c r="Q21" s="23" t="n"/>
+      <c r="R21" s="23" t="n"/>
+      <c r="S21" s="23" t="n"/>
+      <c r="T21" s="23" t="n"/>
+      <c r="U21" s="23" t="n"/>
+      <c r="V21" s="23" t="n"/>
+      <c r="W21" s="23" t="n"/>
+      <c r="X21" s="23" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1" s="11">
-      <c r="A22" s="20" t="n"/>
-      <c r="B22" s="20" t="n"/>
-      <c r="C22" s="20" t="n"/>
-      <c r="D22" s="20" t="n"/>
-      <c r="E22" s="20" t="n"/>
-      <c r="F22" s="20" t="n"/>
-      <c r="G22" s="20" t="n"/>
-      <c r="H22" s="20" t="n"/>
-      <c r="I22" s="20" t="n"/>
-      <c r="J22" s="20" t="n"/>
-      <c r="K22" s="20" t="n"/>
-      <c r="L22" s="20" t="n"/>
-      <c r="M22" s="20" t="n"/>
-      <c r="N22" s="20" t="n"/>
-      <c r="O22" s="20" t="n"/>
-      <c r="P22" s="20" t="n"/>
-      <c r="Q22" s="20" t="n"/>
-      <c r="R22" s="20" t="n"/>
-      <c r="S22" s="20" t="n"/>
-      <c r="T22" s="20" t="n"/>
-      <c r="U22" s="20" t="n"/>
-      <c r="V22" s="20" t="n"/>
-      <c r="W22" s="20" t="n"/>
-      <c r="X22" s="20" t="n"/>
+      <c r="A22" s="23" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+      <c r="H22" s="23" t="n"/>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="23" t="n"/>
+      <c r="L22" s="23" t="n"/>
+      <c r="M22" s="23" t="n"/>
+      <c r="N22" s="23" t="n"/>
+      <c r="O22" s="23" t="n"/>
+      <c r="P22" s="23" t="n"/>
+      <c r="Q22" s="23" t="n"/>
+      <c r="R22" s="23" t="n"/>
+      <c r="S22" s="23" t="n"/>
+      <c r="T22" s="23" t="n"/>
+      <c r="U22" s="23" t="n"/>
+      <c r="V22" s="23" t="n"/>
+      <c r="W22" s="23" t="n"/>
+      <c r="X22" s="23" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="11">
-      <c r="A23" s="20" t="n"/>
-      <c r="B23" s="20" t="n"/>
-      <c r="C23" s="20" t="n"/>
-      <c r="D23" s="20" t="n"/>
-      <c r="E23" s="20" t="n"/>
-      <c r="F23" s="20" t="n"/>
-      <c r="G23" s="20" t="n"/>
-      <c r="H23" s="20" t="n"/>
-      <c r="I23" s="20" t="n"/>
-      <c r="J23" s="20" t="n"/>
-      <c r="K23" s="20" t="n"/>
-      <c r="L23" s="20" t="n"/>
-      <c r="M23" s="20" t="n"/>
-      <c r="N23" s="20" t="n"/>
-      <c r="O23" s="20" t="n"/>
-      <c r="P23" s="20" t="n"/>
-      <c r="Q23" s="20" t="n"/>
-      <c r="R23" s="20" t="n"/>
-      <c r="S23" s="20" t="n"/>
-      <c r="T23" s="20" t="n"/>
-      <c r="U23" s="20" t="n"/>
-      <c r="V23" s="20" t="n"/>
-      <c r="W23" s="20" t="n"/>
-      <c r="X23" s="20" t="n"/>
+      <c r="A23" s="23" t="n"/>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+      <c r="H23" s="23" t="n"/>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="23" t="n"/>
+      <c r="L23" s="23" t="n"/>
+      <c r="M23" s="23" t="n"/>
+      <c r="N23" s="23" t="n"/>
+      <c r="O23" s="23" t="n"/>
+      <c r="P23" s="23" t="n"/>
+      <c r="Q23" s="23" t="n"/>
+      <c r="R23" s="23" t="n"/>
+      <c r="S23" s="23" t="n"/>
+      <c r="T23" s="23" t="n"/>
+      <c r="U23" s="23" t="n"/>
+      <c r="V23" s="23" t="n"/>
+      <c r="W23" s="23" t="n"/>
+      <c r="X23" s="23" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="11">
-      <c r="A24" s="20" t="n"/>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="20" t="n"/>
-      <c r="D24" s="20" t="n"/>
-      <c r="E24" s="20" t="n"/>
-      <c r="F24" s="20" t="n"/>
-      <c r="G24" s="20" t="n"/>
-      <c r="H24" s="20" t="n"/>
-      <c r="I24" s="20" t="n"/>
-      <c r="J24" s="20" t="n"/>
-      <c r="K24" s="20" t="n"/>
-      <c r="L24" s="20" t="n"/>
-      <c r="M24" s="20" t="n"/>
-      <c r="N24" s="20" t="n"/>
-      <c r="O24" s="20" t="n"/>
-      <c r="P24" s="20" t="n"/>
-      <c r="Q24" s="20" t="n"/>
-      <c r="R24" s="20" t="n"/>
-      <c r="S24" s="20" t="n"/>
-      <c r="T24" s="20" t="n"/>
-      <c r="U24" s="20" t="n"/>
-      <c r="V24" s="20" t="n"/>
-      <c r="W24" s="20" t="n"/>
-      <c r="X24" s="20" t="n"/>
+      <c r="A24" s="23" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="n"/>
+      <c r="H24" s="23" t="n"/>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="23" t="n"/>
+      <c r="L24" s="23" t="n"/>
+      <c r="M24" s="23" t="n"/>
+      <c r="N24" s="23" t="n"/>
+      <c r="O24" s="23" t="n"/>
+      <c r="P24" s="23" t="n"/>
+      <c r="Q24" s="23" t="n"/>
+      <c r="R24" s="23" t="n"/>
+      <c r="S24" s="23" t="n"/>
+      <c r="T24" s="23" t="n"/>
+      <c r="U24" s="23" t="n"/>
+      <c r="V24" s="23" t="n"/>
+      <c r="W24" s="23" t="n"/>
+      <c r="X24" s="23" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="11">
-      <c r="A25" s="20" t="n"/>
-      <c r="B25" s="20" t="n"/>
-      <c r="C25" s="20" t="n"/>
-      <c r="D25" s="20" t="n"/>
-      <c r="E25" s="20" t="n"/>
-      <c r="F25" s="20" t="n"/>
-      <c r="G25" s="20" t="n"/>
-      <c r="H25" s="20" t="n"/>
-      <c r="I25" s="20" t="n"/>
-      <c r="J25" s="20" t="n"/>
-      <c r="K25" s="20" t="n"/>
-      <c r="L25" s="20" t="n"/>
-      <c r="M25" s="20" t="n"/>
-      <c r="N25" s="20" t="n"/>
-      <c r="O25" s="20" t="n"/>
-      <c r="P25" s="20" t="n"/>
-      <c r="Q25" s="20" t="n"/>
-      <c r="R25" s="20" t="n"/>
-      <c r="S25" s="20" t="n"/>
-      <c r="T25" s="20" t="n"/>
-      <c r="U25" s="20" t="n"/>
-      <c r="V25" s="20" t="n"/>
-      <c r="W25" s="20" t="n"/>
-      <c r="X25" s="20" t="n"/>
+      <c r="A25" s="23" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+      <c r="H25" s="23" t="n"/>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="23" t="n"/>
+      <c r="L25" s="23" t="n"/>
+      <c r="M25" s="23" t="n"/>
+      <c r="N25" s="23" t="n"/>
+      <c r="O25" s="23" t="n"/>
+      <c r="P25" s="23" t="n"/>
+      <c r="Q25" s="23" t="n"/>
+      <c r="R25" s="23" t="n"/>
+      <c r="S25" s="23" t="n"/>
+      <c r="T25" s="23" t="n"/>
+      <c r="U25" s="23" t="n"/>
+      <c r="V25" s="23" t="n"/>
+      <c r="W25" s="23" t="n"/>
+      <c r="X25" s="23" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="11">
-      <c r="A26" s="20" t="n"/>
-      <c r="B26" s="20" t="n"/>
-      <c r="C26" s="20" t="n"/>
-      <c r="D26" s="20" t="n"/>
-      <c r="E26" s="20" t="n"/>
-      <c r="F26" s="20" t="n"/>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="20" t="n"/>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="20" t="n"/>
-      <c r="K26" s="20" t="n"/>
-      <c r="L26" s="20" t="n"/>
-      <c r="M26" s="20" t="n"/>
-      <c r="N26" s="20" t="n"/>
-      <c r="O26" s="20" t="n"/>
-      <c r="P26" s="20" t="n"/>
-      <c r="Q26" s="20" t="n"/>
-      <c r="R26" s="20" t="n"/>
-      <c r="S26" s="20" t="n"/>
-      <c r="T26" s="20" t="n"/>
-      <c r="U26" s="20" t="n"/>
-      <c r="V26" s="20" t="n"/>
-      <c r="W26" s="20" t="n"/>
-      <c r="X26" s="20" t="n"/>
+      <c r="A26" s="23" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+      <c r="H26" s="23" t="n"/>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="23" t="n"/>
+      <c r="L26" s="23" t="n"/>
+      <c r="M26" s="23" t="n"/>
+      <c r="N26" s="23" t="n"/>
+      <c r="O26" s="23" t="n"/>
+      <c r="P26" s="23" t="n"/>
+      <c r="Q26" s="23" t="n"/>
+      <c r="R26" s="23" t="n"/>
+      <c r="S26" s="23" t="n"/>
+      <c r="T26" s="23" t="n"/>
+      <c r="U26" s="23" t="n"/>
+      <c r="V26" s="23" t="n"/>
+      <c r="W26" s="23" t="n"/>
+      <c r="X26" s="23" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="11">
-      <c r="A27" s="20" t="n"/>
-      <c r="B27" s="20" t="n"/>
-      <c r="C27" s="20" t="n"/>
-      <c r="D27" s="20" t="n"/>
-      <c r="E27" s="20" t="n"/>
-      <c r="F27" s="20" t="n"/>
-      <c r="G27" s="20" t="n"/>
-      <c r="H27" s="20" t="n"/>
-      <c r="I27" s="20" t="n"/>
-      <c r="J27" s="20" t="n"/>
-      <c r="K27" s="20" t="n"/>
-      <c r="L27" s="20" t="n"/>
-      <c r="M27" s="20" t="n"/>
-      <c r="N27" s="20" t="n"/>
-      <c r="O27" s="20" t="n"/>
-      <c r="P27" s="20" t="n"/>
-      <c r="Q27" s="20" t="n"/>
-      <c r="R27" s="20" t="n"/>
-      <c r="S27" s="20" t="n"/>
-      <c r="T27" s="20" t="n"/>
-      <c r="U27" s="20" t="n"/>
-      <c r="V27" s="20" t="n"/>
-      <c r="W27" s="20" t="n"/>
-      <c r="X27" s="20" t="n"/>
+      <c r="A27" s="23" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
+      <c r="H27" s="23" t="n"/>
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="23" t="n"/>
+      <c r="L27" s="23" t="n"/>
+      <c r="M27" s="23" t="n"/>
+      <c r="N27" s="23" t="n"/>
+      <c r="O27" s="23" t="n"/>
+      <c r="P27" s="23" t="n"/>
+      <c r="Q27" s="23" t="n"/>
+      <c r="R27" s="23" t="n"/>
+      <c r="S27" s="23" t="n"/>
+      <c r="T27" s="23" t="n"/>
+      <c r="U27" s="23" t="n"/>
+      <c r="V27" s="23" t="n"/>
+      <c r="W27" s="23" t="n"/>
+      <c r="X27" s="23" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1" s="11">
-      <c r="A28" s="20" t="n"/>
-      <c r="B28" s="20" t="n"/>
-      <c r="C28" s="20" t="n"/>
-      <c r="D28" s="20" t="n"/>
-      <c r="E28" s="20" t="n"/>
-      <c r="F28" s="20" t="n"/>
-      <c r="G28" s="20" t="n"/>
-      <c r="H28" s="20" t="n"/>
-      <c r="I28" s="20" t="n"/>
-      <c r="J28" s="20" t="n"/>
-      <c r="K28" s="20" t="n"/>
-      <c r="L28" s="20" t="n"/>
-      <c r="M28" s="20" t="n"/>
-      <c r="N28" s="20" t="n"/>
-      <c r="O28" s="20" t="n"/>
-      <c r="P28" s="20" t="n"/>
-      <c r="Q28" s="20" t="n"/>
-      <c r="R28" s="20" t="n"/>
-      <c r="S28" s="20" t="n"/>
-      <c r="T28" s="20" t="n"/>
-      <c r="U28" s="20" t="n"/>
-      <c r="V28" s="20" t="n"/>
-      <c r="W28" s="20" t="n"/>
-      <c r="X28" s="20" t="n"/>
+      <c r="A28" s="23" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+      <c r="H28" s="23" t="n"/>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="23" t="n"/>
+      <c r="L28" s="23" t="n"/>
+      <c r="M28" s="23" t="n"/>
+      <c r="N28" s="23" t="n"/>
+      <c r="O28" s="23" t="n"/>
+      <c r="P28" s="23" t="n"/>
+      <c r="Q28" s="23" t="n"/>
+      <c r="R28" s="23" t="n"/>
+      <c r="S28" s="23" t="n"/>
+      <c r="T28" s="23" t="n"/>
+      <c r="U28" s="23" t="n"/>
+      <c r="V28" s="23" t="n"/>
+      <c r="W28" s="23" t="n"/>
+      <c r="X28" s="23" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1" s="11">
-      <c r="A29" s="20" t="n"/>
-      <c r="B29" s="20" t="n"/>
-      <c r="C29" s="20" t="n"/>
-      <c r="D29" s="20" t="n"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="20" t="n"/>
-      <c r="G29" s="20" t="n"/>
-      <c r="H29" s="20" t="n"/>
-      <c r="I29" s="20" t="n"/>
-      <c r="J29" s="20" t="n"/>
-      <c r="K29" s="20" t="n"/>
-      <c r="L29" s="20" t="n"/>
-      <c r="M29" s="20" t="n"/>
-      <c r="N29" s="20" t="n"/>
-      <c r="O29" s="20" t="n"/>
-      <c r="P29" s="20" t="n"/>
-      <c r="Q29" s="20" t="n"/>
-      <c r="R29" s="20" t="n"/>
-      <c r="S29" s="20" t="n"/>
-      <c r="T29" s="20" t="n"/>
-      <c r="U29" s="20" t="n"/>
-      <c r="V29" s="20" t="n"/>
-      <c r="W29" s="20" t="n"/>
-      <c r="X29" s="20" t="n"/>
+      <c r="A29" s="23" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
+      <c r="H29" s="23" t="n"/>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="23" t="n"/>
+      <c r="L29" s="23" t="n"/>
+      <c r="M29" s="23" t="n"/>
+      <c r="N29" s="23" t="n"/>
+      <c r="O29" s="23" t="n"/>
+      <c r="P29" s="23" t="n"/>
+      <c r="Q29" s="23" t="n"/>
+      <c r="R29" s="23" t="n"/>
+      <c r="S29" s="23" t="n"/>
+      <c r="T29" s="23" t="n"/>
+      <c r="U29" s="23" t="n"/>
+      <c r="V29" s="23" t="n"/>
+      <c r="W29" s="23" t="n"/>
+      <c r="X29" s="23" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="11">
-      <c r="A30" s="20" t="n"/>
-      <c r="B30" s="20" t="n"/>
-      <c r="C30" s="20" t="n"/>
-      <c r="D30" s="20" t="n"/>
-      <c r="E30" s="20" t="n"/>
-      <c r="F30" s="20" t="n"/>
-      <c r="G30" s="20" t="n"/>
-      <c r="H30" s="20" t="n"/>
-      <c r="I30" s="20" t="n"/>
-      <c r="J30" s="20" t="n"/>
-      <c r="K30" s="20" t="n"/>
-      <c r="L30" s="20" t="n"/>
-      <c r="M30" s="20" t="n"/>
-      <c r="N30" s="20" t="n"/>
-      <c r="O30" s="20" t="n"/>
-      <c r="P30" s="20" t="n"/>
-      <c r="Q30" s="20" t="n"/>
-      <c r="R30" s="20" t="n"/>
-      <c r="S30" s="20" t="n"/>
-      <c r="T30" s="20" t="n"/>
-      <c r="U30" s="20" t="n"/>
-      <c r="V30" s="20" t="n"/>
-      <c r="W30" s="20" t="n"/>
-      <c r="X30" s="20" t="n"/>
+      <c r="A30" s="23" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="23" t="n"/>
+      <c r="F30" s="23" t="n"/>
+      <c r="G30" s="23" t="n"/>
+      <c r="H30" s="23" t="n"/>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="23" t="n"/>
+      <c r="L30" s="23" t="n"/>
+      <c r="M30" s="23" t="n"/>
+      <c r="N30" s="23" t="n"/>
+      <c r="O30" s="23" t="n"/>
+      <c r="P30" s="23" t="n"/>
+      <c r="Q30" s="23" t="n"/>
+      <c r="R30" s="23" t="n"/>
+      <c r="S30" s="23" t="n"/>
+      <c r="T30" s="23" t="n"/>
+      <c r="U30" s="23" t="n"/>
+      <c r="V30" s="23" t="n"/>
+      <c r="W30" s="23" t="n"/>
+      <c r="X30" s="23" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="11">
-      <c r="A31" s="20" t="n"/>
-      <c r="B31" s="20" t="n"/>
-      <c r="C31" s="20" t="n"/>
-      <c r="D31" s="20" t="n"/>
-      <c r="E31" s="20" t="n"/>
-      <c r="F31" s="20" t="n"/>
-      <c r="G31" s="20" t="n"/>
-      <c r="H31" s="20" t="n"/>
-      <c r="I31" s="20" t="n"/>
-      <c r="J31" s="20" t="n"/>
-      <c r="K31" s="20" t="n"/>
-      <c r="L31" s="20" t="n"/>
-      <c r="M31" s="20" t="n"/>
-      <c r="N31" s="20" t="n"/>
-      <c r="O31" s="20" t="n"/>
-      <c r="P31" s="20" t="n"/>
-      <c r="Q31" s="20" t="n"/>
-      <c r="R31" s="20" t="n"/>
-      <c r="S31" s="20" t="n"/>
-      <c r="T31" s="20" t="n"/>
-      <c r="U31" s="20" t="n"/>
-      <c r="V31" s="20" t="n"/>
-      <c r="W31" s="20" t="n"/>
-      <c r="X31" s="20" t="n"/>
+      <c r="A31" s="23" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="23" t="n"/>
+      <c r="H31" s="23" t="n"/>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="23" t="n"/>
+      <c r="L31" s="23" t="n"/>
+      <c r="M31" s="23" t="n"/>
+      <c r="N31" s="23" t="n"/>
+      <c r="O31" s="23" t="n"/>
+      <c r="P31" s="23" t="n"/>
+      <c r="Q31" s="23" t="n"/>
+      <c r="R31" s="23" t="n"/>
+      <c r="S31" s="23" t="n"/>
+      <c r="T31" s="23" t="n"/>
+      <c r="U31" s="23" t="n"/>
+      <c r="V31" s="23" t="n"/>
+      <c r="W31" s="23" t="n"/>
+      <c r="X31" s="23" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1" s="11">
-      <c r="A32" s="20" t="n"/>
-      <c r="B32" s="20" t="n"/>
-      <c r="C32" s="20" t="n"/>
-      <c r="D32" s="20" t="n"/>
-      <c r="E32" s="20" t="n"/>
-      <c r="F32" s="20" t="n"/>
-      <c r="G32" s="20" t="n"/>
-      <c r="H32" s="20" t="n"/>
-      <c r="I32" s="20" t="n"/>
-      <c r="J32" s="20" t="n"/>
-      <c r="K32" s="20" t="n"/>
-      <c r="L32" s="20" t="n"/>
-      <c r="M32" s="20" t="n"/>
-      <c r="N32" s="20" t="n"/>
-      <c r="O32" s="20" t="n"/>
-      <c r="P32" s="20" t="n"/>
-      <c r="Q32" s="20" t="n"/>
-      <c r="R32" s="20" t="n"/>
-      <c r="S32" s="20" t="n"/>
-      <c r="T32" s="20" t="n"/>
-      <c r="U32" s="20" t="n"/>
-      <c r="V32" s="20" t="n"/>
-      <c r="W32" s="20" t="n"/>
-      <c r="X32" s="20" t="n"/>
+      <c r="A32" s="23" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="23" t="n"/>
+      <c r="F32" s="23" t="n"/>
+      <c r="G32" s="23" t="n"/>
+      <c r="H32" s="23" t="n"/>
+      <c r="I32" s="23" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="23" t="n"/>
+      <c r="L32" s="23" t="n"/>
+      <c r="M32" s="23" t="n"/>
+      <c r="N32" s="23" t="n"/>
+      <c r="O32" s="23" t="n"/>
+      <c r="P32" s="23" t="n"/>
+      <c r="Q32" s="23" t="n"/>
+      <c r="R32" s="23" t="n"/>
+      <c r="S32" s="23" t="n"/>
+      <c r="T32" s="23" t="n"/>
+      <c r="U32" s="23" t="n"/>
+      <c r="V32" s="23" t="n"/>
+      <c r="W32" s="23" t="n"/>
+      <c r="X32" s="23" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="11">
-      <c r="A33" s="20" t="n"/>
-      <c r="B33" s="20" t="n"/>
-      <c r="C33" s="20" t="n"/>
-      <c r="D33" s="20" t="n"/>
-      <c r="E33" s="20" t="n"/>
-      <c r="F33" s="20" t="n"/>
-      <c r="G33" s="20" t="n"/>
-      <c r="H33" s="20" t="n"/>
-      <c r="I33" s="20" t="n"/>
-      <c r="J33" s="20" t="n"/>
-      <c r="K33" s="20" t="n"/>
-      <c r="L33" s="20" t="n"/>
-      <c r="M33" s="20" t="n"/>
-      <c r="N33" s="20" t="n"/>
-      <c r="O33" s="20" t="n"/>
-      <c r="P33" s="20" t="n"/>
-      <c r="Q33" s="20" t="n"/>
-      <c r="R33" s="20" t="n"/>
-      <c r="S33" s="20" t="n"/>
-      <c r="T33" s="20" t="n"/>
-      <c r="U33" s="20" t="n"/>
-      <c r="V33" s="20" t="n"/>
-      <c r="W33" s="20" t="n"/>
-      <c r="X33" s="20" t="n"/>
+      <c r="A33" s="23" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
+      <c r="H33" s="23" t="n"/>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="23" t="n"/>
+      <c r="L33" s="23" t="n"/>
+      <c r="M33" s="23" t="n"/>
+      <c r="N33" s="23" t="n"/>
+      <c r="O33" s="23" t="n"/>
+      <c r="P33" s="23" t="n"/>
+      <c r="Q33" s="23" t="n"/>
+      <c r="R33" s="23" t="n"/>
+      <c r="S33" s="23" t="n"/>
+      <c r="T33" s="23" t="n"/>
+      <c r="U33" s="23" t="n"/>
+      <c r="V33" s="23" t="n"/>
+      <c r="W33" s="23" t="n"/>
+      <c r="X33" s="23" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="6">
@@ -1794,8 +1852,8 @@
       <formula1>"Immédiate,Date précise,Préavis"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="X4:X33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"En poste ALIMA,En attente de poste,En poste autre ONG,En poste hors humanitaire"</formula1>
+    <dataValidation sqref="Y4:Y33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Expatrié,National"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/templates/Cap_Huma_Modele_Import_Talents_VIERGE.xlsx
+++ b/templates/Cap_Huma_Modele_Import_Talents_VIERGE.xlsx
@@ -540,7 +540,7 @@
     <row r="11" ht="23.85" customHeight="1" s="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Prénom, Nom et Email sont obligatoires pour chaque ligne. Code Pool est obligatoire UNIQUEMENT si la colonne Type de staff est vide ou vaut « Expatrié » — dans ce cas il doit correspondre exactement à un pool déjà existant dans Cap Huma. Pour un staff national (voir plus bas), laissez Code Pool vide.</t>
+          <t>Prénom, Nom et Email sont obligatoires pour chaque ligne. Code Pool est obligatoire UNIQUEMENT si la colonne Type de staff est vide ou vaut « Expatrié » — dans ce cas il doit correspondre exactement à un pool déjà existant dans Cap Huma. Pour un staff national (voir plus bas), laissez Code Pool vide. Le champ Statut (colonne X) est également obligatoire pour chaque ligne — voir la section dédiée ci-dessous.</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
     <row r="15" ht="23.85" customHeight="1" s="11">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Genre, Niveau d'études, Visa valide, Nombre de missions ALIMA et Type de disponibilité ont une liste déroulante dans le fichier — choisissez toujours une valeur de la liste, ne tapez jamais de texte libre dans ces colonnes.</t>
+          <t>Genre, Niveau d'études, Visa valide, Nombre de missions ALIMA, Type de disponibilité et Statut ont une liste déroulante dans le fichier — choisissez toujours une valeur de la liste, ne tapez jamais de texte libre dans ces colonnes.</t>
         </is>
       </c>
     </row>
@@ -587,23 +587,20 @@
       </c>
     </row>
     <row r="23" ht="46.25" customHeight="1" s="11"/>
-    <row r="26"/>
     <row r="27" ht="15" customHeight="1" s="11">
       <c r="A27" s="15" t="inlineStr">
         <is>
-          <t>⚠️ Champ Statut — laisser vide</t>
+          <t>⚠️ Champ Statut — obligatoire</t>
         </is>
       </c>
     </row>
     <row r="28" ht="35.05" customHeight="1" s="11">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>Les 4 valeurs exactes acceptées par la base pour ce champ n'ont pas encore été confirmées avec certitude au moment de la création de ce modèle. Par sécurité, laissez cette colonne VIDE — chaque talent importé prendra automatiquement le statut par défaut (« En attente de poste »), et vous pourrez l'ajuster ensuite dans Cap Huma si besoin. Ne pas deviner de valeur : une valeur incorrecte ferait échouer l'import de la ligne entière.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30"/>
+          <t>Ce champ est désormais obligatoire pour chaque ligne (une cellule vide fait échouer l'import de la ligne). Une liste déroulante propose les 4 valeurs acceptées par la base : « En attente de poste », « En poste ALIMA », « En poste autre ONG », « En poste hors humanitaire ». Pour l'import initial de nouveaux talents, mettez systématiquement « En attente de poste » : vous pourrez ensuite ajuster le statut réel de chacun directement dans Cap Huma si besoin. Ne tapez jamais de texte libre dans cette colonne, choisissez toujours une valeur de la liste.</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="15" customHeight="1" s="11"/>
     <row r="32" ht="23.85" customHeight="1" s="11">
       <c r="A32" s="14" t="inlineStr">
@@ -619,8 +616,6 @@
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="14" t="inlineStr">
         <is>
@@ -792,7 +787,7 @@
       </c>
       <c r="X1" s="18" t="inlineStr">
         <is>
-          <t>Statut (laisser vide)</t>
+          <t>Statut*</t>
         </is>
       </c>
       <c r="Y1" s="18" t="inlineStr">
@@ -1042,7 +1037,11 @@
       </c>
       <c r="V3" s="22" t="n"/>
       <c r="W3" s="22" t="n"/>
-      <c r="X3" s="22" t="n"/>
+      <c r="X3" s="22" t="inlineStr">
+        <is>
+          <t>En attente de poste</t>
+        </is>
+      </c>
       <c r="Y3" s="22" t="inlineStr">
         <is>
           <t>Expatrié</t>
@@ -1831,7 +1830,7 @@
       <c r="X33" s="23" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="E4:E33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"H,F"</formula1>
       <formula2>0</formula2>
@@ -1855,6 +1854,9 @@
     <dataValidation sqref="Y4:Y33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Expatrié,National"</formula1>
     </dataValidation>
+    <dataValidation sqref="X4:X33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="Statut invalide" error="Choisissez une valeur dans la liste : En attente de poste, En poste ALIMA, En poste autre ONG, En poste hors humanitaire" type="list">
+      <formula1>"En attente de poste,En poste ALIMA,En poste autre ONG,En poste hors humanitaire"</formula1>
+    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
